--- a/data/trans_orig/KIDMED_R3-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/KIDMED_R3-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>20300</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>14631</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>26504</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>33,69%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>24,28%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>43,98%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>32500</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>22516</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>40880</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>45,52%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>31,53%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>57,25%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>24088</t>
+          <t>24174</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16739</t>
+          <t>18751</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31223</t>
+          <t>29665</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>56588</t>
+          <t>44474</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45187</t>
+          <t>36715</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>68384</t>
+          <t>52706</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>45,76%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>39963</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>33759</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>45632</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>66,31%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>56,02%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>75,72%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>38900</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>30520</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>48884</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>54,48%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>42,75%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>68,47%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>50519</t>
+          <t>30748</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>43384</t>
+          <t>25257</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>57868</t>
+          <t>36171</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>89419</t>
+          <t>70712</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>77623</t>
+          <t>62480</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>100820</t>
+          <t>78471</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>61,39%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>54,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>68,13%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>42013</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>32402</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>53339</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>36,55%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>28,19%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>46,4%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>40717</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>17688</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>55505</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>32,41%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>14,08%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>44,17%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>47147</t>
+          <t>40313</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36473</t>
+          <t>31721</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>59265</t>
+          <t>48448</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>87864</t>
+          <t>82326</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>61602</t>
+          <t>69539</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>105634</t>
+          <t>96328</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>44,95%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>72938</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>61612</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>82549</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>63,45%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>53,6%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>71,81%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>84932</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>70144</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>107961</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>67,59%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>55,83%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>85,92%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>79276</t>
+          <t>59020</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>67158</t>
+          <t>50885</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>89950</t>
+          <t>67612</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>51,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>164207</t>
+          <t>131958</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>146437</t>
+          <t>117956</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>190469</t>
+          <t>144745</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>67,55%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>40639</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>34740</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>45198</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>70,92%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>60,63%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>78,88%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>27392</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>21719</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>33704</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>49,31%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>39,1%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>60,67%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>44703</t>
+          <t>26130</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38099</t>
+          <t>20759</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49850</t>
+          <t>31929</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>72095</t>
+          <t>66769</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>63232</t>
+          <t>58435</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>80980</t>
+          <t>74758</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>59,93%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>52,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>67,1%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>16660</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>22559</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>29,08%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>21,12%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>39,37%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>28160</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>21848</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>33833</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>50,69%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>39,33%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>60,9%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19930</t>
+          <t>27982</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14783</t>
+          <t>22183</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26534</t>
+          <t>33353</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>51,71%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>48090</t>
+          <t>44642</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>39205</t>
+          <t>36653</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>56953</t>
+          <t>52976</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>47,55%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>36315</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>21300</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>46108</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>52,02%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>30,51%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>66,04%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>41075</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>33700</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>48181</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>58,95%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>48,36%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>69,14%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>39123</t>
+          <t>42381</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21894</t>
+          <t>34494</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50403</t>
+          <t>50070</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>60,15%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>80197</t>
+          <t>78696</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>58418</t>
+          <t>61763</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>92660</t>
+          <t>91205</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>56,1%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>65,02%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>33501</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>23708</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>48516</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>47,98%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>33,96%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>69,49%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>28607</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>21501</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>35982</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>41,05%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>30,86%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>51,64%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>36244</t>
+          <t>28081</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>24964</t>
+          <t>20392</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>53473</t>
+          <t>35968</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>51,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>64852</t>
+          <t>61582</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>52389</t>
+          <t>49073</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>86631</t>
+          <t>78515</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>43,9%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>55,97%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>38949</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>36477</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>98,41%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>92,16%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>32877</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>30446</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>33887</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>96,13%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>89,02%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>99,08%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>40097</t>
+          <t>34076</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>37566</t>
+          <t>31338</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35116</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>72974</t>
+          <t>73025</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>70162</t>
+          <t>69489</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>74344</t>
+          <t>74389</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,25%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>7,84%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>1323</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>313</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>3754</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>3,87%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>10,98%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>254</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3153</t>
+          <t>4032</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>1924</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>560</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4757</t>
+          <t>5460</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>23542</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>18396</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>28852</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>49,87%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>38,97%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>61,11%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>15854</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>11312</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>21477</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>35,79%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>25,54%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>48,49%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>27414</t>
+          <t>15988</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21165</t>
+          <t>11614</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>33640</t>
+          <t>21169</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>43268</t>
+          <t>39530</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>35698</t>
+          <t>32421</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>51146</t>
+          <t>47013</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>43,2%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>51,38%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>23667</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>18357</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>28813</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>50,13%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>38,89%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>61,03%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>28436</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>22813</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>32978</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>64,21%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>51,51%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>74,46%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>26368</t>
+          <t>28298</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>20142</t>
+          <t>23117</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>32617</t>
+          <t>32672</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>49,03%</t>
+          <t>63,9%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>73,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>54804</t>
+          <t>51965</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>46926</t>
+          <t>44482</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>62374</t>
+          <t>59074</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>64,57%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>92707</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>82061</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>102744</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>65,95%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>58,38%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>73,09%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>87614</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>77909</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>96820</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>70,83%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>62,98%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>78,27%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>101392</t>
+          <t>86406</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>85218</t>
+          <t>76760</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>113196</t>
+          <t>94351</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>189006</t>
+          <t>179114</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>171864</t>
+          <t>164866</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>203206</t>
+          <t>192491</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>62,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>73,36%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>47864</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>37827</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>58510</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>34,05%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>26,91%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>41,62%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>36082</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>26876</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>45787</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>29,17%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>21,73%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>37,02%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>53652</t>
+          <t>35416</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>41848</t>
+          <t>27471</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>69826</t>
+          <t>45062</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>89734</t>
+          <t>83280</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>75534</t>
+          <t>69903</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>106876</t>
+          <t>97528</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>37,17%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3121,72 +3121,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>144557</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>137428</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>149776</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>91,99%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>87,46%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>95,32%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>115985</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>108703</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>120863</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>90,15%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>84,49%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>93,94%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>142153</t>
+          <t>124172</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>135254</t>
+          <t>115560</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>147159</t>
+          <t>129677</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>258137</t>
+          <t>268729</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>248827</t>
+          <t>258309</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>265822</t>
+          <t>276171</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,61%</t>
         </is>
       </c>
     </row>
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>12579</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>7360</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>19708</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>8,01%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>4,68%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>12,54%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>12680</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>7802</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>19962</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>9,85%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>6,06%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>15,51%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>12006</t>
+          <t>13728</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7000</t>
+          <t>8223</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>18905</t>
+          <t>22340</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>24686</t>
+          <t>26307</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>17001</t>
+          <t>18865</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>33996</t>
+          <t>36727</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,45%</t>
         </is>
       </c>
     </row>
@@ -3347,57 +3347,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3464,72 +3464,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>439023</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>411473</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>463185</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>63,92%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>59,91%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>67,44%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>585</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>394014</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>342979</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>421661</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>60,33%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>52,51%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>64,56%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>466116</t>
+          <t>393640</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>435981</t>
+          <t>374528</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>495052</t>
+          <t>412911</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>860130</t>
+          <t>832662</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>796725</t>
+          <t>798965</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>899449</t>
+          <t>863679</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>61,22%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>66,18%</t>
         </is>
       </c>
     </row>
@@ -3577,72 +3577,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>247801</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>223639</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>275351</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>36,08%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>32,56%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>40,09%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>330</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>259120</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>231473</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>310155</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>39,67%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>35,44%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>47,49%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>327</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>278617</t>
+          <t>224568</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>249681</t>
+          <t>205297</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>308752</t>
+          <t>243680</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>537737</t>
+          <t>472369</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>498418</t>
+          <t>441352</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>601142</t>
+          <t>506066</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>38,78%</t>
         </is>
       </c>
     </row>
@@ -3690,57 +3690,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
